--- a/artfynd/A 38459-2025 artfynd.xlsx
+++ b/artfynd/A 38459-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136550164</v>
       </c>
       <c r="B2" t="n">
-        <v>102694</v>
+        <v>102697</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136547517</v>
       </c>
       <c r="B3" t="n">
-        <v>98271</v>
+        <v>98274</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 38459-2025 artfynd.xlsx
+++ b/artfynd/A 38459-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136550164</v>
       </c>
       <c r="B2" t="n">
-        <v>102697</v>
+        <v>102698</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136547517</v>
       </c>
       <c r="B3" t="n">
-        <v>98274</v>
+        <v>98275</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 38459-2025 artfynd.xlsx
+++ b/artfynd/A 38459-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136550164</v>
       </c>
       <c r="B2" t="n">
-        <v>102698</v>
+        <v>102703</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136547517</v>
       </c>
       <c r="B3" t="n">
-        <v>98275</v>
+        <v>98280</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 38459-2025 artfynd.xlsx
+++ b/artfynd/A 38459-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136550164</v>
       </c>
       <c r="B2" t="n">
-        <v>102703</v>
+        <v>102705</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136547517</v>
       </c>
       <c r="B3" t="n">
-        <v>98280</v>
+        <v>98282</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 38459-2025 artfynd.xlsx
+++ b/artfynd/A 38459-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136550164</v>
       </c>
       <c r="B2" t="n">
-        <v>102705</v>
+        <v>102711</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136547517</v>
       </c>
       <c r="B3" t="n">
-        <v>98282</v>
+        <v>98288</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 38459-2025 artfynd.xlsx
+++ b/artfynd/A 38459-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136550164</v>
       </c>
       <c r="B2" t="n">
-        <v>102711</v>
+        <v>102713</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136547517</v>
       </c>
       <c r="B3" t="n">
-        <v>98288</v>
+        <v>98290</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 38459-2025 artfynd.xlsx
+++ b/artfynd/A 38459-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136550164</v>
       </c>
       <c r="B2" t="n">
-        <v>102713</v>
+        <v>102714</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136547517</v>
       </c>
       <c r="B3" t="n">
-        <v>98290</v>
+        <v>98291</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 38459-2025 artfynd.xlsx
+++ b/artfynd/A 38459-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136550164</v>
       </c>
       <c r="B2" t="n">
-        <v>102714</v>
+        <v>102720</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136547517</v>
       </c>
       <c r="B3" t="n">
-        <v>98291</v>
+        <v>98297</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 38459-2025 artfynd.xlsx
+++ b/artfynd/A 38459-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136550164</v>
       </c>
       <c r="B2" t="n">
-        <v>102720</v>
+        <v>102724</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136547517</v>
       </c>
       <c r="B3" t="n">
-        <v>98297</v>
+        <v>98301</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 38459-2025 artfynd.xlsx
+++ b/artfynd/A 38459-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136550164</v>
       </c>
       <c r="B2" t="n">
-        <v>102724</v>
+        <v>102726</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136547517</v>
       </c>
       <c r="B3" t="n">
-        <v>98301</v>
+        <v>98303</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 38459-2025 artfynd.xlsx
+++ b/artfynd/A 38459-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136550164</v>
       </c>
       <c r="B2" t="n">
-        <v>102726</v>
+        <v>102728</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Mikael Andersson</t>
+          <t>Mikael Andersson, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -789,7 +789,7 @@
         <v>136547517</v>
       </c>
       <c r="B3" t="n">
-        <v>98303</v>
+        <v>98305</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 38459-2025 artfynd.xlsx
+++ b/artfynd/A 38459-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136550164</v>
       </c>
       <c r="B2" t="n">
-        <v>102728</v>
+        <v>102741</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Mikael Andersson, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Mikael Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -789,7 +789,7 @@
         <v>136547517</v>
       </c>
       <c r="B3" t="n">
-        <v>98305</v>
+        <v>98318</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 38459-2025 artfynd.xlsx
+++ b/artfynd/A 38459-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136550164</v>
       </c>
       <c r="B2" t="n">
-        <v>102741</v>
+        <v>102743</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136547517</v>
       </c>
       <c r="B3" t="n">
-        <v>98318</v>
+        <v>98320</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
